--- a/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A09_A10_세부요청표_20261028_담당자반영.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/ISO14001_증빙수집요청_20261028/담당자반영_20261028/ISO14001_A09_A10_세부요청표_20261028_담당자반영.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 권고일 2026-11-06</t>
+          <t>A-09 환경목표·월별 성과 2026 실적 — 담당 역할: 환경/총무 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 권고일 2026-11-06</t>
+          <t>A-10 환경 교육·비상대응 훈련 실적 — 담당 역할: 환경/안전 · 담당자: 박철호 부장 · 대체자: 이광재 부장 · 권고일 2026-11-06</t>
         </is>
       </c>
     </row>
